--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104736_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104736_W31.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.3147</v>
+        <v>9.947699999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9717</v>
+        <v>7.2391</v>
       </c>
       <c r="F2" t="n">
-        <v>2.343</v>
+        <v>2.7086</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1491</v>
+        <v>6.141</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4135</v>
+        <v>4.4038</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7356</v>
+        <v>1.7372</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8297</v>
+        <v>5.8084</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3384</v>
+        <v>4.319</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4913</v>
+        <v>1.4895</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3194</v>
+        <v>0.3326</v>
       </c>
       <c r="N2" t="n">
-        <v>0.075</v>
+        <v>0.0848</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2443</v>
+        <v>0.2477</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4496</v>
+        <v>-0.8</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1105</v>
+        <v>-0.8087</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3391</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>5.2968</v>
+        <v>5.2896</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5244</v>
+        <v>4.5157</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5036</v>
+        <v>5.4366</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2624</v>
+        <v>4.3571</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2412</v>
+        <v>1.0795</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5305</v>
+        <v>4.5307</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3622</v>
+        <v>2.3633</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1683</v>
+        <v>2.1674</v>
       </c>
       <c r="J3" t="n">
-        <v>6.7675</v>
+        <v>6.7523</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9401</v>
+        <v>3.93</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8274</v>
+        <v>2.8223</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.237</v>
+        <v>-2.2216</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5779</v>
+        <v>-1.5667</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6591</v>
+        <v>-0.6549</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3901</v>
+        <v>-0.4599</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3692</v>
+        <v>-1.2571</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9791</v>
+        <v>0.7972</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>B. JEFFERSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6061</v>
+        <v>3.9572</v>
       </c>
       <c r="E4" t="n">
-        <v>2.484</v>
+        <v>1.3493</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1222</v>
+        <v>2.6079</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7705</v>
+        <v>2.5287</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3299</v>
+        <v>-1.0487</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1003</v>
+        <v>3.5774</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3891</v>
+        <v>1.9095</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6679</v>
+        <v>-1.6795</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0571</v>
+        <v>3.589</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3813</v>
+        <v>0.6192</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3381</v>
+        <v>0.6308</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0433</v>
+        <v>-0.0116</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0447</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0447</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0416</v>
+        <v>-0.5503</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0948</v>
+        <v>-0.718</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0532</v>
+        <v>0.1677</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2507</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. JEFFERSON</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.521</v>
+        <v>3.3935</v>
       </c>
       <c r="E5" t="n">
-        <v>1.18</v>
+        <v>2.1914</v>
       </c>
       <c r="F5" t="n">
-        <v>2.341</v>
+        <v>1.2021</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5324</v>
+        <v>2.7732</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0519</v>
+        <v>-0.3252</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5843</v>
+        <v>3.0983</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9228</v>
+        <v>2.3844</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.6755</v>
+        <v>-0.669</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5983</v>
+        <v>3.0534</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6096</v>
+        <v>0.3887</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.3438</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.014</v>
+        <v>0.0449</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8175</v>
+        <v>2.0487</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8175</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9883</v>
+        <v>-0.1811</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9023</v>
+        <v>-0.193</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.0119</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1594</v>
+        <v>-1.2472</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1594</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4034</v>
+        <v>2.093</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9195</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.484</v>
+        <v>1.1821</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6441</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0369</v>
+        <v>1.0342</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3928</v>
+        <v>-0.3916</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4949</v>
+        <v>1.4884</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4577</v>
+        <v>1.4511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8508</v>
+        <v>-0.8458</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4208</v>
+        <v>-0.4169</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4301</v>
+        <v>-0.4289</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3281</v>
+        <v>0.0163</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1893</v>
+        <v>-0.1906</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5173</v>
+        <v>0.2069</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5597</v>
+        <v>1.2441</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5948</v>
+        <v>1.1167</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0351</v>
+        <v>0.1273</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7361</v>
+        <v>0.7365</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1014</v>
+        <v>-0.1006</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8375</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0835</v>
+        <v>1.0797</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1841</v>
+        <v>-0.1864</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2676</v>
+        <v>1.2661</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3474</v>
+        <v>-0.3432</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0857</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4301</v>
+        <v>-0.4289</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>0.142</v>
+        <v>-0.1754</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5113</v>
+        <v>0.037</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3692</v>
+        <v>-0.2124</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6293</v>
+        <v>0.9008</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0607</v>
+        <v>1.0353</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4313</v>
+        <v>-0.1345</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7189</v>
+        <v>2.7184</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5966</v>
+        <v>0.5972</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1224</v>
+        <v>2.1212</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9623</v>
+        <v>3.9507</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7687</v>
+        <v>1.7614</v>
       </c>
       <c r="L8" t="n">
-        <v>2.1936</v>
+        <v>2.1893</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2434</v>
+        <v>-1.2323</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1722</v>
+        <v>-1.1642</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0712</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8411999999999999</v>
+        <v>-0.5609</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.7482</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.1873</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2705</v>
+        <v>-0.2719</v>
       </c>
       <c r="E9" t="n">
-        <v>0.048</v>
+        <v>0.0452</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3184</v>
+        <v>-0.3171</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0274</v>
+        <v>0.0268</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3629</v>
+        <v>0.362</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3355</v>
+        <v>-0.3351</v>
       </c>
       <c r="J9" t="n">
-        <v>0.573</v>
+        <v>0.5716</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5357</v>
+        <v>0.5343</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3728</v>
+        <v>-0.3724</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1388</v>
+        <v>-0.1394</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1388</v>
+        <v>-0.1394</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. ALOCEN</t>
+          <t>K. ROBERTSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2403</v>
+        <v>-0.9895</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0753</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.165</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5805</v>
+        <v>-3.6236</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1465</v>
+        <v>-4.4518</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.434</v>
+        <v>0.8282</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7025</v>
+        <v>-1.9885</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0864</v>
+        <v>-2.9862</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7889</v>
+        <v>0.9977</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.878</v>
+        <v>-1.6351</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2329</v>
+        <v>-1.4656</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6451</v>
+        <v>-0.1695</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4544</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6816</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2966</v>
+        <v>-0.7725</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3281</v>
+        <v>-0.7692</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0315</v>
+        <v>-0.0033</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0913</v>
+        <v>2.7237</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0913</v>
+        <v>3.8132</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>C. ALOCEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2713</v>
+        <v>-1.1216</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3368</v>
+        <v>-0.9637</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0655</v>
+        <v>-0.1579</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3803</v>
+        <v>-1.5769</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0398</v>
+        <v>-0.1439</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.42</v>
+        <v>-1.433</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2263</v>
+        <v>-0.7035</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4381</v>
+        <v>0.0862</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.6644</v>
+        <v>-0.7896</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.154</v>
+        <v>-0.8734</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3983</v>
+        <v>-0.2301</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2443</v>
+        <v>-0.6433</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1359</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1359</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6099</v>
+        <v>-0.1789</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1105</v>
+        <v>-0.2115</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7204</v>
+        <v>0.0327</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6369</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. ROBERTSON</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4556</v>
+        <v>-2.0402</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2515</v>
+        <v>-2.162</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2041</v>
+        <v>0.1218</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6266</v>
+        <v>-1.3762</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.4555</v>
+        <v>0.0452</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8288</v>
+        <v>-1.4214</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9822</v>
+        <v>-1.2349</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.9828</v>
+        <v>0.4342</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0006</v>
+        <v>-1.6691</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6444</v>
+        <v>-0.1412</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4727</v>
+        <v>-0.389</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1718</v>
+        <v>0.2477</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6816</v>
+        <v>1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8175</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2387</v>
+        <v>-0.168</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9527</v>
+        <v>-0.9271</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2859</v>
+        <v>0.7591</v>
       </c>
       <c r="V12" t="n">
-        <v>2.7281</v>
+        <v>-1.6342</v>
       </c>
       <c r="W12" t="n">
-        <v>3.8194</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0913</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5395</v>
+        <v>-4.4446</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7225</v>
+        <v>-2.7305</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.817</v>
+        <v>-1.7141</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.3462</v>
+        <v>-1.3424</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.4494</v>
+        <v>-1.4451</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1032</v>
+        <v>0.1027</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0342</v>
+        <v>-0.036</v>
       </c>
       <c r="K13" t="n">
-        <v>0.121</v>
+        <v>0.1207</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1551</v>
+        <v>-0.1566</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.312</v>
+        <v>-1.3064</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5703</v>
+        <v>-1.5658</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2583</v>
+        <v>0.2593</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.5903</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5118</v>
+        <v>-0.4193</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4164</v>
+        <v>-0.4182</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0953</v>
+        <v>-0.0011</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.7606</v>
+        <v>18.1051</v>
       </c>
       <c r="E14" t="n">
-        <v>12.135</v>
+        <v>12.3061</v>
       </c>
       <c r="F14" t="n">
-        <v>5.625999999999999</v>
+        <v>5.7989</v>
       </c>
       <c r="G14" t="n">
-        <v>12.1754</v>
+        <v>12.1788</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2773</v>
+        <v>1.290400000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>10.8981</v>
+        <v>10.8885</v>
       </c>
       <c r="J14" t="n">
-        <v>20.07760000000001</v>
+        <v>19.9821</v>
       </c>
       <c r="K14" t="n">
-        <v>7.175800000000001</v>
+        <v>7.1158</v>
       </c>
       <c r="L14" t="n">
-        <v>12.9021</v>
+        <v>12.8664</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.9023</v>
+        <v>-7.8032</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.8987</v>
+        <v>-5.825600000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.004</v>
+        <v>-1.978</v>
       </c>
       <c r="P14" t="n">
-        <v>4.5437</v>
+        <v>4.5528</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.3593</v>
+        <v>-11.3817</v>
       </c>
       <c r="R14" t="n">
-        <v>15.9032</v>
+        <v>15.9343</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.7335</v>
+        <v>-4.3894</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.656200000000001</v>
+        <v>-6.344</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9229</v>
+        <v>1.9547</v>
       </c>
       <c r="V14" t="n">
-        <v>5.775</v>
+        <v>5.762899999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>10.0728</v>
+        <v>10.0494</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.2978</v>
+        <v>-4.2865</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9349</v>
+        <v>5.6106</v>
       </c>
       <c r="E15" t="n">
-        <v>5.494</v>
+        <v>4.5305</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4409</v>
+        <v>1.0801</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0202</v>
+        <v>3.016</v>
       </c>
       <c r="H15" t="n">
-        <v>4.0641</v>
+        <v>4.0586</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0439</v>
+        <v>-1.0426</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6578</v>
+        <v>3.6458</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3722</v>
+        <v>4.3609</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6298</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3081</v>
+        <v>-0.3023</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3295</v>
+        <v>-0.3275</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1419</v>
+        <v>0.8223</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7449</v>
+        <v>-0.2047</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3969</v>
+        <v>1.027</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1607</v>
+        <v>2.0412</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2984</v>
+        <v>2.1592</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1377</v>
+        <v>-0.118</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3834</v>
+        <v>0.3826</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3953</v>
+        <v>1.3906</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0119</v>
+        <v>-1.008</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3967</v>
+        <v>2.386</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6884</v>
+        <v>1.6785</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7083</v>
+        <v>0.7075</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0133</v>
+        <v>-2.0034</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2931</v>
+        <v>-0.2879</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7203</v>
+        <v>-1.7155</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.5903</v>
+        <v>-1.5934</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.8651</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1449</v>
+        <v>-0.2676</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1262</v>
+        <v>1.1327</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4775</v>
+        <v>1.4764</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0525</v>
+        <v>1.6058</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3665</v>
+        <v>-0.6125</v>
       </c>
       <c r="F17" t="n">
-        <v>2.419</v>
+        <v>2.2183</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4913</v>
+        <v>0.4954</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7536</v>
+        <v>-0.75</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2449</v>
+        <v>1.2455</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9018</v>
+        <v>0.8976</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2307</v>
+        <v>0.2273</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6711</v>
+        <v>0.6703</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4104</v>
+        <v>-0.4022</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9843</v>
+        <v>-0.9774</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5739</v>
+        <v>0.5752</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>1.334</v>
+        <v>0.8827</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0948</v>
+        <v>-0.1443</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2392</v>
+        <v>1.027</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. ALDERETE</t>
+          <t>P. MILLS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2695</v>
+        <v>0.1783</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2385</v>
+        <v>0.3474</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.031</v>
+        <v>-0.1692</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4718</v>
+        <v>-1.963</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0594</v>
+        <v>-1.7256</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5312</v>
+        <v>-0.2374</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2474</v>
+        <v>0.8313</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1728</v>
+        <v>-0.5903</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0746</v>
+        <v>1.4216</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7192</v>
+        <v>-2.7943</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8866000000000001</v>
+        <v>-1.1353</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6058</v>
+        <v>-1.659</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4544</v>
+        <v>1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6816</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>0.453</v>
+        <v>-0.1546</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2587</v>
+        <v>-0.5718</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7117</v>
+        <v>0.4171</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.705</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MILLS</t>
+          <t>H. ALDERETE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7881</v>
+        <v>-0.0278</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1002</v>
+        <v>0.1143</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6879</v>
+        <v>-0.142</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9558</v>
+        <v>-0.4658</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7228</v>
+        <v>1.0622</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.233</v>
+        <v>-1.528</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.2468</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5807</v>
+        <v>0.1724</v>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8051</v>
+        <v>-0.7127</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1421</v>
+        <v>0.8898</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.663</v>
+        <v>-1.6025</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5903</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8175</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1276</v>
+        <v>0.6853</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0411</v>
+        <v>0.095</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.5903</v>
       </c>
       <c r="V19" t="n">
-        <v>0.705</v>
+        <v>-0.7025</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3188</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3862</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9505</v>
+        <v>-0.8649</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4178</v>
+        <v>1.1753</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3683</v>
+        <v>-2.0401</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3201</v>
+        <v>-1.3118</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5891</v>
+        <v>-0.5837</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.731</v>
+        <v>-0.7281</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5122</v>
+        <v>1.5101</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2074</v>
+        <v>0.2068</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3048</v>
+        <v>1.3033</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8323</v>
+        <v>-2.8219</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7965</v>
+        <v>-0.7906</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.0358</v>
+        <v>-2.0314</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.7641</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1328</v>
+        <v>-0.1072</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5553</v>
+        <v>0.8713</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="21">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.326</v>
+        <v>-1.2638</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9798</v>
+        <v>-0.9815</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3462</v>
+        <v>-0.2823</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1595</v>
+        <v>-1.1592</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9444</v>
+        <v>-0.9448</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7716</v>
+        <v>-0.7724</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7716</v>
+        <v>-0.7724</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3878</v>
+        <v>-0.3868</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1666</v>
+        <v>-0.1046</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2082</v>
+        <v>-0.2091</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0416</v>
+        <v>0.1046</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7961</v>
+        <v>-1.4882</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2903</v>
+        <v>0.5187</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0864</v>
+        <v>-2.0068</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8461</v>
+        <v>-0.8447</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1232</v>
+        <v>0.1235</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0538</v>
+        <v>1.0485</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6936</v>
+        <v>1.6892</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6398</v>
+        <v>-0.6407</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8999</v>
+        <v>-1.8932</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5703</v>
+        <v>-1.5658</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3295</v>
+        <v>-0.3275</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0625</v>
+        <v>0.238</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5363</v>
+        <v>-0.3022</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4738</v>
+        <v>0.5402</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7963</v>
+        <v>-1.792</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7963</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9223</v>
+        <v>-4.2546</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8871</v>
+        <v>-2.5514</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0352</v>
+        <v>-1.7032</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1001</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4328</v>
+        <v>1.433</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5319</v>
+        <v>-1.5331</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6531</v>
+        <v>0.6427</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2676</v>
+        <v>1.2615</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6145</v>
+        <v>-0.6188</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7521</v>
+        <v>-0.7428</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1652</v>
+        <v>0.1715</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9174</v>
+        <v>-0.9143</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.732</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0411</v>
+        <v>-0.6902</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3091</v>
+        <v>0.6251</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.7281</v>
+        <v>-2.7237</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.7281</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7385</v>
+        <v>-4.9871</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7659</v>
+        <v>-4.3066</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9726</v>
+        <v>-0.6805</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.6197</v>
+        <v>-4.6211</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.2217</v>
+        <v>-2.2226</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.398</v>
+        <v>-2.3985</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.0243</v>
+        <v>-3.0334</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.4471</v>
+        <v>-2.4519</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5772</v>
+        <v>-0.5816</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5954</v>
+        <v>-1.5877</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2254</v>
+        <v>0.2292</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.8208</v>
+        <v>-1.8169</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4373</v>
+        <v>0.317</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3785</v>
+        <v>0.0926</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0588</v>
+        <v>0.2243</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8673</v>
+        <v>-5.9925</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8822</v>
+        <v>-3.0269</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9851</v>
+        <v>-2.9655</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.6926</v>
+        <v>-4.6995</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.7566</v>
+        <v>-2.7645</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.936</v>
+        <v>-1.935</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.4292</v>
+        <v>-1.4458</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1562</v>
+        <v>-1.1698</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.273</v>
+        <v>-0.276</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.2634</v>
+        <v>-3.2536</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.6004</v>
+        <v>-1.5946</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.663</v>
+        <v>-1.659</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>1.1202</v>
+        <v>1.0045</v>
       </c>
       <c r="T25" t="n">
-        <v>0.341</v>
+        <v>0.2203</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7792</v>
+        <v>0.7842</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9318</v>
+        <v>-0.9317</v>
       </c>
       <c r="W25" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.2503</v>
+        <v>-7.5242</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.9061</v>
+        <v>-3.1654</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.3442</v>
+        <v>-4.3588</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.9055</v>
+        <v>-0.9077</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3636</v>
+        <v>-0.3671</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5419</v>
+        <v>-0.5406</v>
       </c>
       <c r="J26" t="n">
-        <v>1.8555</v>
+        <v>1.8461</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2218</v>
+        <v>1.2131</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6338</v>
+        <v>0.633</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.7611</v>
+        <v>-2.7538</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.5854</v>
+        <v>-1.5802</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.1757</v>
+        <v>-1.1736</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.5437</v>
+        <v>-4.5526</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.6797</v>
+        <v>-5.6908</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5409</v>
+        <v>0.2728</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3725</v>
+        <v>0.1345</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1684</v>
+        <v>0.1383</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.3419</v>
+        <v>-2.3367</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.8875</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-17.7605</v>
+        <v>-16.9672</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.6258</v>
+        <v>-5.7989</v>
       </c>
       <c r="F27" t="n">
-        <v>-12.1347</v>
+        <v>-11.168</v>
       </c>
       <c r="G27" t="n">
-        <v>-12.1753</v>
+        <v>-12.1789</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.277000000000001</v>
+        <v>-1.290399999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-10.8982</v>
+        <v>-10.8884</v>
       </c>
       <c r="J27" t="n">
-        <v>7.902500000000001</v>
+        <v>7.803299999999998</v>
       </c>
       <c r="K27" t="n">
-        <v>5.8989</v>
+        <v>5.825299999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>2.0038</v>
+        <v>1.9779</v>
       </c>
       <c r="M27" t="n">
-        <v>-20.0776</v>
+        <v>-19.9822</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.175800000000001</v>
+        <v>-7.116000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>-12.9019</v>
+        <v>-12.8664</v>
       </c>
       <c r="P27" t="n">
-        <v>-4.5437</v>
+        <v>-4.552700000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>-15.9032</v>
+        <v>-15.934</v>
       </c>
       <c r="R27" t="n">
-        <v>11.3593</v>
+        <v>11.3818</v>
       </c>
       <c r="S27" t="n">
-        <v>4.7334</v>
+        <v>5.527500000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.922799999999999</v>
+        <v>-1.9547</v>
       </c>
       <c r="U27" t="n">
-        <v>6.6561</v>
+        <v>7.4821</v>
       </c>
       <c r="V27" t="n">
-        <v>-5.7749</v>
+        <v>-5.7629</v>
       </c>
       <c r="W27" t="n">
-        <v>4.2976</v>
+        <v>4.2864</v>
       </c>
       <c r="X27" t="n">
-        <v>-10.0726</v>
+        <v>-10.0493</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104736_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104736_W31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-4.2865</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104736_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-10.0493</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
